--- a/reporte_consolidado.xlsx
+++ b/reporte_consolidado.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29197</v>
+        <v>34071</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.079608917236328</v>
+        <v>8.591348648071289</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9084494982361202</v>
+        <v>0.8091925684599807</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02339281433023941</v>
+        <v>0.03492706407208476</v>
       </c>
     </row>
   </sheetData>
